--- a/reports/빅딜/history/2026-05-07/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-05-07/빅딜_league_mgf_report.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블루Moon!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">섹시미!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">재앙!$A$1:$J$25</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="496">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,118 +80,118 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>464조 4003억 246만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.05.07</t>
+  </si>
+  <si>
+    <t>섹시미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%B9%EC%8B%9C%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>493조 6117억 6736만</t>
+  </si>
+  <si>
+    <t>가입문의 듸우로 귓주세요! 2d 미접속,길컨 미참여 강퇴 / 1조이상 / 철새x / 접률우대</t>
+  </si>
+  <si>
+    <t>듸우</t>
+  </si>
+  <si>
+    <t>재앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9E%AC%EC%95%99</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>12위</t>
+  </si>
+  <si>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>470조 4553억 7674만</t>
+  </si>
+  <si>
+    <t>- 길드 컨텐츠 필참, 오픈챗 운영중 - 함께 성장하실분 환영합니다 :) - 가입 문의 '빛나는및나리'</t>
+  </si>
+  <si>
+    <t>빛나는및나리</t>
+  </si>
+  <si>
+    <t>블루Moon</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A3%A8Moon</t>
+  </si>
+  <si>
+    <t>Scania 36</t>
+  </si>
+  <si>
     <t>354</t>
   </si>
   <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>464조 4003억 246만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.05.07</t>
-  </si>
-  <si>
-    <t>섹시미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%B9%EC%8B%9C%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>493조 6117억 6736만</t>
-  </si>
-  <si>
-    <t>가입문의 듸우로 귓주세요! 2d 미접속,길컨 미참여 강퇴 / 1조이상 / 철새x / 접률우대</t>
-  </si>
-  <si>
-    <t>듸우</t>
-  </si>
-  <si>
-    <t>재앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9E%AC%EC%95%99</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>12위</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>470조 4553억 7674만</t>
-  </si>
-  <si>
-    <t>- 길드 컨텐츠 필참, 오픈챗 운영중 - 함께 성장하실분 환영합니다 :) - 가입 문의 '빛나는및나리'</t>
-  </si>
-  <si>
-    <t>빛나는및나리</t>
-  </si>
-  <si>
-    <t>블루Moon</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A3%A8Moon</t>
-  </si>
-  <si>
-    <t>Scania 36</t>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>464조 7648억 9514만</t>
+  </si>
+  <si>
+    <t>3조이상 문의 귓 주세요.</t>
+  </si>
+  <si>
+    <t>환불5천</t>
+  </si>
+  <si>
+    <t>비련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
   </si>
   <si>
     <t>353</t>
   </si>
   <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>464조 7648억 9514만</t>
-  </si>
-  <si>
-    <t>3조이상 문의 귓 주세요.</t>
-  </si>
-  <si>
-    <t>환불5천</t>
-  </si>
-  <si>
-    <t>비련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
     <t>29위</t>
   </si>
   <si>
-    <t>466조 182억 7111만</t>
+    <t>466조 9065억 7092만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 3조 이상 일일기부 300+ 길컨 참여자</t>
@@ -248,6 +248,18 @@
     <t>2</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>61조 9128억 5605만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -263,18 +275,6 @@
     <t>60조 9099억 5542만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>48조 3007억 2445만</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -449,6 +449,33 @@
     <t>16</t>
   </si>
   <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>7조 9942억 9967만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>7조 7632억 9651만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
@@ -458,7 +485,7 @@
     <t>6조 9243억 6066만</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -467,13 +494,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>6조 188억 8756만</t>
   </si>
   <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -485,7 +509,7 @@
     <t>6조 72억 9036만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -497,7 +521,19 @@
     <t>5조 7027억 3580만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>5조 3996억 7064만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -509,7 +545,7 @@
     <t>5조 1673억 305만</t>
   </si>
   <si>
-    <t>21</t>
+    <t>24</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -524,7 +560,7 @@
     <t>5조 1451억 4249만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>25</t>
   </si>
   <si>
     <t>여븨</t>
@@ -536,7 +572,7 @@
     <t>4조 8791억 7843만</t>
   </si>
   <si>
-    <t>23</t>
+    <t>26</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -548,7 +584,31 @@
     <t>3조 4127억 6119만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>3조 3267억 9445만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 8773억 332만</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -563,7 +623,7 @@
     <t>2조 7967억 8402만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>30</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -803,9 +863,6 @@
     <t>3조 6456억 7004만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>꾸준맨</t>
   </si>
   <si>
@@ -815,9 +872,6 @@
     <t>3조 3890억 8703만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>예능돼지</t>
   </si>
   <si>
@@ -827,9 +881,6 @@
     <t>3조 9129만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>아이싱</t>
   </si>
   <si>
@@ -839,9 +890,6 @@
     <t>2조 8667억 2388만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>돌빠</t>
   </si>
   <si>
@@ -1376,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>13조 5792억 6362만</t>
+    <t>14조 806억 5546만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1412,7 +1460,7 @@
     <t>https://mgf.gg/contents/character.php?n=Scope</t>
   </si>
   <si>
-    <t>5조 371억 5749만</t>
+    <t>5조 778억 5430만</t>
   </si>
   <si>
     <t>하콩치</t>
@@ -2106,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2190,25 +2238,25 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="G3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2219,25 +2267,25 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>81</v>
@@ -2330,7 +2378,7 @@
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>96</v>
@@ -2365,7 +2413,7 @@
         <v>101</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>102</v>
@@ -2650,13 +2698,13 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2667,25 +2715,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>147</v>
@@ -2717,7 +2765,7 @@
         <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>151</v>
@@ -2746,10 +2794,10 @@
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>155</v>
@@ -2778,10 +2826,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>159</v>
@@ -2810,13 +2858,13 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2827,16 +2875,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -2845,10 +2893,10 @@
         <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2859,28 +2907,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2891,28 +2939,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="H25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -2923,35 +2971,195 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J26" s="2" t="s">
+      <c r="I31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -2978,6 +3186,11 @@
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3038,13 +3251,13 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -3053,10 +3266,10 @@
         <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3070,25 +3283,25 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3099,7 +3312,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -3108,10 +3321,10 @@
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>119</v>
@@ -3120,7 +3333,7 @@
         <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3134,13 +3347,13 @@
         <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -3149,10 +3362,10 @@
         <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3166,13 +3379,13 @@
         <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -3184,7 +3397,7 @@
         <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3198,13 +3411,13 @@
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -3216,7 +3429,7 @@
         <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3230,13 +3443,13 @@
         <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -3248,7 +3461,7 @@
         <v>96</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3262,13 +3475,13 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
@@ -3277,10 +3490,10 @@
         <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3294,13 +3507,13 @@
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -3312,7 +3525,7 @@
         <v>96</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3326,13 +3539,13 @@
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -3341,10 +3554,10 @@
         <v>119</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3358,25 +3571,25 @@
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3390,25 +3603,25 @@
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3422,13 +3635,13 @@
         <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -3440,7 +3653,7 @@
         <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3454,13 +3667,13 @@
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -3472,7 +3685,7 @@
         <v>124</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3486,13 +3699,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -3504,7 +3717,7 @@
         <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3518,13 +3731,13 @@
         <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -3536,7 +3749,7 @@
         <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3547,16 +3760,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -3568,7 +3781,7 @@
         <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3582,13 +3795,13 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -3600,7 +3813,7 @@
         <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3614,13 +3827,13 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -3632,7 +3845,7 @@
         <v>91</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3646,13 +3859,13 @@
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -3664,7 +3877,7 @@
         <v>91</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3678,13 +3891,13 @@
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -3696,7 +3909,7 @@
         <v>124</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3707,16 +3920,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -3728,7 +3941,7 @@
         <v>124</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3739,16 +3952,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -3760,7 +3973,7 @@
         <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3771,16 +3984,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -3789,10 +4002,10 @@
         <v>119</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3803,16 +4016,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -3821,10 +4034,10 @@
         <v>85</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3835,16 +4048,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -3856,7 +4069,7 @@
         <v>124</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3867,28 +4080,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3899,28 +4112,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3931,16 +4144,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>270</v>
+        <v>193</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
@@ -3949,10 +4162,10 @@
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4056,19 +4269,19 @@
         <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>119</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4082,13 +4295,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -4100,7 +4313,7 @@
         <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4111,16 +4324,16 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
@@ -4132,7 +4345,7 @@
         <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4146,13 +4359,13 @@
         <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -4164,7 +4377,7 @@
         <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4178,13 +4391,13 @@
         <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -4196,7 +4409,7 @@
         <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4210,13 +4423,13 @@
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -4228,7 +4441,7 @@
         <v>91</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4242,13 +4455,13 @@
         <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -4257,10 +4470,10 @@
         <v>119</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4274,25 +4487,25 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4306,13 +4519,13 @@
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -4324,7 +4537,7 @@
         <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4338,25 +4551,25 @@
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4370,25 +4583,25 @@
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4402,13 +4615,13 @@
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -4420,7 +4633,7 @@
         <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4434,25 +4647,25 @@
         <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4466,13 +4679,13 @@
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -4484,7 +4697,7 @@
         <v>124</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4498,13 +4711,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -4516,7 +4729,7 @@
         <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4530,13 +4743,13 @@
         <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -4545,10 +4758,10 @@
         <v>101</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4559,16 +4772,16 @@
         <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -4580,7 +4793,7 @@
         <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4594,13 +4807,13 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -4612,7 +4825,7 @@
         <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4626,13 +4839,13 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -4644,7 +4857,7 @@
         <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4658,13 +4871,13 @@
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -4676,7 +4889,7 @@
         <v>124</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4690,25 +4903,25 @@
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4719,16 +4932,16 @@
         <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -4737,10 +4950,10 @@
         <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4751,16 +4964,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -4769,10 +4982,10 @@
         <v>85</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4783,16 +4996,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -4801,10 +5014,10 @@
         <v>69</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4897,13 +5110,13 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -4915,7 +5128,7 @@
         <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4929,25 +5142,25 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4958,16 +5171,16 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
@@ -4976,10 +5189,10 @@
         <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4993,13 +5206,13 @@
         <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -5011,7 +5224,7 @@
         <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5025,13 +5238,13 @@
         <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -5043,7 +5256,7 @@
         <v>124</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5057,13 +5270,13 @@
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -5075,7 +5288,7 @@
         <v>124</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5089,13 +5302,13 @@
         <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -5107,7 +5320,7 @@
         <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5121,25 +5334,25 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5153,13 +5366,13 @@
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -5171,7 +5384,7 @@
         <v>124</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5185,13 +5398,13 @@
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -5203,7 +5416,7 @@
         <v>124</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5217,25 +5430,25 @@
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5249,13 +5462,13 @@
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -5264,10 +5477,10 @@
         <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5287,10 +5500,10 @@
         <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>85</v>
@@ -5299,7 +5512,7 @@
         <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5313,13 +5526,13 @@
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -5328,10 +5541,10 @@
         <v>85</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5345,13 +5558,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -5360,10 +5573,10 @@
         <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5377,13 +5590,13 @@
         <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -5392,10 +5605,10 @@
         <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5406,16 +5619,16 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -5424,10 +5637,10 @@
         <v>133</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5441,25 +5654,25 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5473,25 +5686,25 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5505,13 +5718,13 @@
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -5520,10 +5733,10 @@
         <v>101</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5537,13 +5750,13 @@
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -5552,10 +5765,10 @@
         <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5566,16 +5779,16 @@
         <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -5584,10 +5797,10 @@
         <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5598,16 +5811,16 @@
         <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -5616,10 +5829,10 @@
         <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5630,16 +5843,16 @@
         <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -5648,10 +5861,10 @@
         <v>119</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5662,16 +5875,16 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -5680,10 +5893,10 @@
         <v>85</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5694,16 +5907,16 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -5712,10 +5925,10 @@
         <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5726,16 +5939,16 @@
         <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
@@ -5744,10 +5957,10 @@
         <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5758,16 +5971,16 @@
         <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -5776,10 +5989,10 @@
         <v>85</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5876,13 +6089,13 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -5891,10 +6104,10 @@
         <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5908,13 +6121,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -5926,7 +6139,7 @@
         <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5937,16 +6150,16 @@
         <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
@@ -5958,7 +6171,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5972,13 +6185,13 @@
         <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -5990,7 +6203,7 @@
         <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6010,19 +6223,19 @@
         <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>119</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6036,13 +6249,13 @@
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -6054,7 +6267,7 @@
         <v>91</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6068,13 +6281,13 @@
         <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -6086,7 +6299,7 @@
         <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6100,13 +6313,13 @@
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
@@ -6118,7 +6331,7 @@
         <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6132,13 +6345,13 @@
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -6150,7 +6363,7 @@
         <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6164,13 +6377,13 @@
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -6182,7 +6395,7 @@
         <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6196,13 +6409,13 @@
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
@@ -6211,10 +6424,10 @@
         <v>85</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6228,13 +6441,13 @@
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -6246,7 +6459,7 @@
         <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6260,25 +6473,25 @@
         <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6292,13 +6505,13 @@
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -6307,10 +6520,10 @@
         <v>133</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6324,13 +6537,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -6339,10 +6552,10 @@
         <v>85</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6356,25 +6569,25 @@
         <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6385,16 +6598,16 @@
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -6403,10 +6616,10 @@
         <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
